--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -499,7 +499,7 @@
         <v>44733</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">

--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -499,7 +499,7 @@
         <v>44733</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">

--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">

--- a/output/publications.xlsx
+++ b/output/publications.xlsx
@@ -470,7 +470,7 @@
         <v>44006</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
